--- a/QA_Deliverables_Aabid.xlsx
+++ b/QA_Deliverables_Aabid.xlsx
@@ -158,6 +158,366 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="1609725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="1609725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="1857375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="1857375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="1609725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="1857375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="1857375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="1609725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="1857375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="1857375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="1609725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="1857375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="1857375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2857500" cy="1857375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -449,7 +809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -459,6 +819,8 @@
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="44.85714285714285" customWidth="1" min="8" max="8"/>
+    <col width="44.85714285714285" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -497,8 +859,23 @@
           <t>Snapshot Ref</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Screenshot 1</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Screenshot 2</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Screenshot 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="131.75" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>TC-01</t>
@@ -537,7 +914,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="151.25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>TC-02</t>
@@ -575,7 +952,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="151.25" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TC-03</t>
@@ -613,7 +990,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="131.75" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>TC-04</t>
@@ -650,7 +1027,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="151.25" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>TC-05</t>
@@ -687,7 +1064,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="151.25" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>TC-06</t>
@@ -724,7 +1101,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="131.75" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>TC-07</t>
@@ -761,7 +1138,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="151.25" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>TC-08</t>
@@ -798,7 +1175,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="151.25" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>TC-09</t>
@@ -912,7 +1289,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="131.75" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>TC-12</t>
@@ -1026,7 +1403,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="151.25" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>TC-15</t>
@@ -1065,6 +1442,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1074,7 +1452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1085,6 +1463,7 @@
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="44.85714285714285" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1128,8 +1507,23 @@
           <t>Snapshot Proof</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Screenshot 1</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Screenshot 2</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Screenshot 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="151.25" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>DEF-001</t>
@@ -1171,7 +1565,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="151.25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>DEF-002</t>
@@ -1215,6 +1609,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
